--- a/90/food/kp2026.xlsx
+++ b/90/food/kp2026.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF13"/>
+  <dimension ref="A1:AF23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.85546875" customWidth="1" style="11" min="1" max="1"/>
@@ -513,7 +513,7 @@
       </c>
       <c r="B1" s="14" t="inlineStr">
         <is>
-          <t>МБОУ «Многопрофильный центр образования им. А.А. Кадырова» г. Грозного</t>
+          <t xml:space="preserve">	МБОУ «Многопрофильный центр образования им. А.А. Кадырова» г. Грозного</t>
         </is>
       </c>
       <c r="C1" s="16" t="n"/>
@@ -551,8 +551,10 @@
           <t>Год</t>
         </is>
       </c>
-      <c r="AD1" s="15" t="n">
-        <v>2026</v>
+      <c r="AD1" s="15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
       </c>
       <c r="AE1" s="17" t="n"/>
       <c r="AF1" s="1" t="n"/>
@@ -1441,6 +1443,13 @@
       </c>
       <c r="AF13" s="4" t="n"/>
     </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="AD1:AE1"/>

--- a/90/food/kp2026.xlsx
+++ b/90/food/kp2026.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF23"/>
+  <dimension ref="A1:AF13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.85546875" customWidth="1" style="11" min="1" max="1"/>
@@ -1443,13 +1443,6 @@
       </c>
       <c r="AF13" s="4" t="n"/>
     </row>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="AD1:AE1"/>

--- a/90/food/kp2026.xlsx
+++ b/90/food/kp2026.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF13"/>
+  <dimension ref="A1:AF23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.85546875" customWidth="1" style="11" min="1" max="1"/>
@@ -1443,6 +1443,13 @@
       </c>
       <c r="AF13" s="4" t="n"/>
     </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="AD1:AE1"/>
